--- a/outputs/clinic4/performance_summary.xlsx
+++ b/outputs/clinic4/performance_summary.xlsx
@@ -3014,7 +3014,6 @@
           <t>l1</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3035,9 +3034,6 @@
           <t>0.451</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>0.731</t>
@@ -3058,9 +3054,6 @@
           <t>0.225</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3081,9 +3074,6 @@
           <t>0.196</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>0.665</t>
@@ -3104,9 +3094,6 @@
           <t>0.225</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3172,7 +3159,6 @@
           <t>l2</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3193,9 +3179,6 @@
           <t>0.298</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>0.660</t>
@@ -3216,9 +3199,6 @@
           <t>0.283</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3239,9 +3219,6 @@
           <t>0.107</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>0.649</t>
@@ -3262,9 +3239,6 @@
           <t>0.283</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3330,7 +3304,6 @@
           <t>l2</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3351,9 +3324,6 @@
           <t>0.167</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>0.648</t>
@@ -3374,9 +3344,6 @@
           <t>0.078</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3555,17 +3522,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.777</t>
+          <t>0.757</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.578</t>
+          <t>0.598</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.474</t>
+          <t>0.486</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3548,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2700</v>
+        <v>2716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3595,17 +3562,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>0.674</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.588</t>
+          <t>0.596</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.474</t>
+          <t>0.486</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3693,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1478</v>
+        <v>1484</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3735,17 +3702,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.673</t>
+          <t>0.661</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.648</t>
+          <t>0.647</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.597</t>
+          <t>0.578</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -4062,21 +4029,21 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6909</v>
+        <v>6938</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.671</t>
+          <t>0.672</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.680</t>
+          <t>0.681</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -4212,7 +4179,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6909</v>
+        <v>6938</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4221,12 +4188,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.668</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.789</t>
+          <t>0.790</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -4548,7 +4515,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2700</v>
+        <v>2716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4562,12 +4529,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.743</t>
+          <t>0.744</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.524</t>
+          <t>0.526</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -4693,7 +4660,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1478</v>
+        <v>1484</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4702,17 +4669,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>0.663</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.740</t>
+          <t>0.741</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.526</t>
+          <t>0.516</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -5034,11 +5001,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6909</v>
+        <v>6938</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -5048,7 +5015,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.727</t>
+          <t>0.728</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -5184,7 +5151,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6909</v>
+        <v>6938</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -5193,12 +5160,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>0.659</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.553</t>
+          <t>0.555</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -5520,7 +5487,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2700</v>
+        <v>2716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -5529,7 +5496,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.664</t>
+          <t>0.669</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -5539,7 +5506,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.586</t>
+          <t>0.594</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -5665,7 +5632,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1478</v>
+        <v>1484</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -5674,17 +5641,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>0.637</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>0.658</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.658</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>0.555</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -6461,17 +6428,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.751</t>
+          <t>0.710</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.563</t>
+          <t>0.614</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>0.302</t>
         </is>
       </c>
     </row>
@@ -6487,31 +6454,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6909</v>
+        <v>6938</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.661</t>
+          <t>0.662</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.646</t>
+          <t>0.596</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.586</t>
+          <t>0.629</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>0.302</t>
         </is>
       </c>
     </row>
@@ -6632,7 +6599,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6909</v>
+        <v>6938</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6641,12 +6608,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.637</t>
+          <t>0.638</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>0.659</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -6968,7 +6935,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2700</v>
+        <v>2716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -6977,7 +6944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.662</t>
+          <t>0.665</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -6987,7 +6954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.501</t>
+          <t>0.515</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -7113,7 +7080,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1478</v>
+        <v>1484</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -7122,17 +7089,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.662</t>
+          <t>0.639</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.532</t>
+          <t>0.531</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.687</t>
+          <t>0.658</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -7454,21 +7421,21 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6909</v>
+        <v>6938</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.662</t>
+          <t>0.663</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.676</t>
+          <t>0.677</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -7604,7 +7571,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6909</v>
+        <v>6938</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -7613,12 +7580,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.641</t>
+          <t>0.642</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.724</t>
+          <t>0.725</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -7940,7 +7907,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2700</v>
+        <v>2716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -7949,7 +7916,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.670</t>
+          <t>0.673</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -7959,7 +7926,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>0.479</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -8085,7 +8052,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1478</v>
+        <v>1484</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -8094,7 +8061,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.670</t>
+          <t>0.659</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8421,21 +8388,21 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6909</v>
+        <v>6938</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.668</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.650</t>
+          <t>0.652</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -8571,7 +8538,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6909</v>
+        <v>6938</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -8580,12 +8547,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.655</t>
+          <t>0.656</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.644</t>
+          <t>0.646</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -8907,7 +8874,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2700</v>
+        <v>2716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -8916,17 +8883,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.665</t>
+          <t>0.670</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>0.552</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.679</t>
+          <t>0.683</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -9052,7 +9019,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1478</v>
+        <v>1484</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -9061,7 +9028,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.666</t>
+          <t>0.653</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -9071,7 +9038,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.604</t>
+          <t>0.589</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -9388,21 +9355,21 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6909</v>
+        <v>6938</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.666</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.521</t>
+          <t>0.524</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -9538,7 +9505,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6909</v>
+        <v>6938</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -9547,12 +9514,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.656</t>
+          <t>0.657</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>0.372</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -9848,7 +9815,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.793</t>
+          <t>0.791</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -9874,7 +9841,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2700</v>
+        <v>2716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -9893,7 +9860,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.610</t>
+          <t>0.605</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -10019,7 +9986,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1478</v>
+        <v>1484</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -10028,7 +9995,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.677</t>
+          <t>0.664</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -10038,7 +10005,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.620</t>
+          <t>0.602</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -10339,7 +10306,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>0.277</t>
         </is>
       </c>
     </row>
@@ -10355,31 +10322,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6909</v>
+        <v>6938</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.673</t>
+          <t>0.674</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.674</t>
+          <t>0.675</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>0.594</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>0.277</t>
         </is>
       </c>
     </row>
@@ -10505,7 +10472,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6909</v>
+        <v>6938</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -10514,12 +10481,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.676</t>
+          <t>0.677</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.742</t>
+          <t>0.743</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -10841,7 +10808,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2700</v>
+        <v>2716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -10850,17 +10817,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.665</t>
+          <t>0.669</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.790</t>
+          <t>0.789</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>0.463</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -10986,7 +10953,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1478</v>
+        <v>1484</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -10995,7 +10962,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.680</t>
+          <t>0.657</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -11005,7 +10972,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>0.398</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -11803,21 +11770,21 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6909</v>
+        <v>6938</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.669</t>
+          <t>0.670</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>0.686</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -11927,7 +11894,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.660</t>
+          <t>0.659</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -11948,7 +11915,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6909</v>
+        <v>6938</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -11957,12 +11924,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>0.659</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.555</t>
+          <t>0.557</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -12284,7 +12251,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2700</v>
+        <v>2716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -12298,12 +12265,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>0.740</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.537</t>
+          <t>0.541</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -12408,7 +12375,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.519</t>
+          <t>0.516</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -12429,7 +12396,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1478</v>
+        <v>1484</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -12438,17 +12405,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.691</t>
+          <t>0.671</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.762</t>
+          <t>0.763</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.494</t>
+          <t>0.496</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -12770,11 +12737,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6909</v>
+        <v>6938</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -12784,7 +12751,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.730</t>
+          <t>0.731</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -12915,7 +12882,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6909</v>
+        <v>6938</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -12924,12 +12891,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.672</t>
+          <t>0.673</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.590</t>
+          <t>0.592</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -13256,7 +13223,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2700</v>
+        <v>2716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -13270,12 +13237,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>0.740</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.537</t>
+          <t>0.541</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -13401,7 +13368,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1478</v>
+        <v>1484</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -13410,17 +13377,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.691</t>
+          <t>0.670</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.710</t>
+          <t>0.712</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.553</t>
+          <t>0.559</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -13709,6 +13676,9 @@
           <t>0.451</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>0.738</t>
@@ -13729,6 +13699,9 @@
           <t>0.443</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13742,13 +13715,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6909</v>
+        <v>6938</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.195</t>
-        </is>
-      </c>
+          <t>0.196</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>0.673</t>
@@ -13756,7 +13732,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.725</t>
+          <t>0.726</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -13769,6 +13745,9 @@
           <t>0.443</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13834,6 +13813,7 @@
           <t>l2</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13854,6 +13834,9 @@
           <t>0.298</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>0.675</t>
@@ -13874,6 +13857,9 @@
           <t>0.231</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13887,21 +13873,24 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6909</v>
+        <v>6938</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>0.107</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.671</t>
+          <t>0.672</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.635</t>
+          <t>0.636</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -13914,6 +13903,9 @@
           <t>0.231</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13979,6 +13971,7 @@
           <t>l2</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13999,6 +13992,9 @@
           <t>0.167</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>0.620</t>
@@ -14019,6 +14015,9 @@
           <t>0.084</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/clinic4/performance_summary.xlsx
+++ b/outputs/clinic4/performance_summary.xlsx
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2716</v>
+        <v>3006</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -661,17 +661,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>0.660</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>0.665</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.664</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.576</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1484</v>
+        <v>1668</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -806,17 +806,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.637</t>
+          <t>0.620</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.705</t>
+          <t>0.693</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.493</t>
+          <t>0.465</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3522,17 +3522,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.757</t>
+          <t>0.777</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.598</t>
+          <t>0.578</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.486</t>
+          <t>0.474</t>
         </is>
       </c>
     </row>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2716</v>
+        <v>3006</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3557,22 +3557,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.679</t>
+          <t>0.672</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.674</t>
+          <t>0.693</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.596</t>
+          <t>0.574</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.486</t>
+          <t>0.474</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1484</v>
+        <v>1668</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3702,17 +3702,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.661</t>
+          <t>0.647</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.647</t>
+          <t>0.635</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.578</t>
+          <t>0.543</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3976,6 +3976,7 @@
           <t>l1</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3996,6 +3997,9 @@
           <t>0.451</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>0.739</t>
@@ -4016,6 +4020,9 @@
           <t>0.273</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4029,26 +4036,29 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6938</v>
+        <v>7546</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.196</t>
-        </is>
-      </c>
+          <t>0.199</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.672</t>
+          <t>0.671</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.681</t>
+          <t>0.683</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.588</t>
+          <t>0.586</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -4056,6 +4066,9 @@
           <t>0.273</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4146,6 +4159,9 @@
           <t>0.298</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>0.701</t>
@@ -4166,6 +4182,9 @@
           <t>0.418</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4179,26 +4198,29 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6938</v>
+        <v>7546</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.107</t>
-        </is>
-      </c>
+          <t>0.111</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.668</t>
+          <t>0.664</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.790</t>
+          <t>0.787</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>0.433</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -4206,6 +4228,9 @@
           <t>0.418</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4271,6 +4296,7 @@
           <t>l1</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4291,6 +4317,9 @@
           <t>0.167</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>0.684</t>
@@ -4311,6 +4340,9 @@
           <t>0.100</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5968,26 +6000,26 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6938</v>
+        <v>7546</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.199</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.662</t>
+          <t>0.663</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.644</t>
+          <t>0.650</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.589</t>
+          <t>0.586</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -6118,26 +6150,26 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6938</v>
+        <v>7546</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>0.111</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>0.631</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.531</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>0.638</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.536</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0.642</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -13676,9 +13708,6 @@
           <t>0.451</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>0.738</t>
@@ -13699,9 +13728,6 @@
           <t>0.443</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13722,9 +13748,6 @@
           <t>0.196</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>0.673</t>
@@ -13745,9 +13768,6 @@
           <t>0.443</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13813,7 +13833,6 @@
           <t>l2</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13834,9 +13853,6 @@
           <t>0.298</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>0.675</t>
@@ -13857,9 +13873,6 @@
           <t>0.231</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13880,9 +13893,6 @@
           <t>0.107</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>0.672</t>
@@ -13903,9 +13913,6 @@
           <t>0.231</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13971,7 +13978,6 @@
           <t>l2</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13992,9 +13998,6 @@
           <t>0.167</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>0.620</t>
@@ -14015,9 +14018,6 @@
           <t>0.084</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
